--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_360_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_360_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>2</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>2</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>2</v>
@@ -1926,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2315,16 +2315,16 @@
         <v>31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" t="n">
         <v>7</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
@@ -3043,16 +3043,16 @@
         <v>123</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="X26" t="n">
         <v>26</v>
@@ -3511,7 +3511,7 @@
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3906,10 +3906,10 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X33" t="n">
         <v>3</v>
@@ -4096,10 +4096,10 @@
         <v>31</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5804,16 +5804,16 @@
         <v>70</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X43" t="n">
         <v>16</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_360_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_360_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>14</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,14 +1543,14 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>1</v>
       </c>
       <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="n">
         <v>3</v>
       </c>
-      <c r="Y20" t="n">
-        <v>4</v>
-      </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,10 +2327,10 @@
         <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>4</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3055,14 +3055,14 @@
         <v>17</v>
       </c>
       <c r="X26" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="Y26" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3912,14 +3912,14 @@
         <v>4</v>
       </c>
       <c r="X33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA33" t="n">
@@ -4108,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -5816,14 +5816,14 @@
         <v>4</v>
       </c>
       <c r="X43" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA43" t="n">
